--- a/artfynd/A 50759-2022 artfynd.xlsx
+++ b/artfynd/A 50759-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50759-2022 artfynd.xlsx
+++ b/artfynd/A 50759-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>100859672</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558385.7365586436</v>
+        <v>558386</v>
       </c>
       <c r="R2" t="n">
-        <v>6314756.314080857</v>
+        <v>6314756</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -757,19 +752,9 @@
           <t>2022-05-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100859671</v>
+        <v>100859674</v>
       </c>
       <c r="B3" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,43 +797,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nyemåla 6, Sm</t>
+          <t>Nyemåla 5, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558385.7365586436</v>
+        <v>558354</v>
       </c>
       <c r="R3" t="n">
-        <v>6314756.314080857</v>
+        <v>6314687</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,24 +863,14 @@
           <t>2022-05-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-05-07</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre gnagspår på tallåga</t>
+          <t>Spelplats för 1-2tuppar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,12 +905,7 @@
         <v>100859675</v>
       </c>
       <c r="B4" t="n">
-        <v>26597</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>25768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558366.3615556011</v>
+        <v>558366</v>
       </c>
       <c r="R4" t="n">
-        <v>6314619.221337424</v>
+        <v>6314619</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1009,19 +974,9 @@
           <t>2022-05-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,6 +1005,238 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100859673</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57794</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nyemåla 5, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>558461</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6314632</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-05-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-05-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Några visslingar sen tyst</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Tallskog blockigmark och blåbär</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100859671</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nyemåla 6, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>558386</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6314756</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-05-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-05-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre gnagspår på tallåga</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Tallskog blockigmark och blåbär</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50759-2022 artfynd.xlsx
+++ b/artfynd/A 50759-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100859672</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100859674</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100859675</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100859673</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,8 +1262,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100859671</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>